--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487570_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487570_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8721</v>
+        <v>3.5046</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6464</v>
+        <v>3.5997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2257</v>
+        <v>-0.0951</v>
       </c>
       <c r="G2" t="n">
         <v>3.3309</v>
@@ -610,13 +610,13 @@
         <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4801</v>
+        <v>2.1126</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3212</v>
+        <v>1.2745</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1589</v>
+        <v>0.8381</v>
       </c>
       <c r="V2" t="n">
         <v>0.9988</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3805</v>
+        <v>1.7054</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3454</v>
+        <v>0.5595</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0351</v>
+        <v>1.1459</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7682</v>
+        <v>0.1947</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1209</v>
+        <v>2.5292</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6474</v>
+        <v>-2.3344</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7934</v>
+        <v>0.4448</v>
       </c>
       <c r="K3" t="n">
-        <v>1.298</v>
+        <v>2.9312</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4954</v>
+        <v>-2.4865</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9749</v>
+        <v>-0.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8228</v>
+        <v>-0.4021</v>
       </c>
       <c r="O3" t="n">
         <v>0.152</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2052</v>
+        <v>-0.4479</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1557</v>
+        <v>0.1147</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0495</v>
+        <v>-0.5625</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6136</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9638</v>
+        <v>1.4358</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5824</v>
+        <v>0.787</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3814</v>
+        <v>0.6488</v>
       </c>
       <c r="G4" t="n">
         <v>-0.636</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4093</v>
+        <v>0.8813</v>
       </c>
       <c r="T4" t="n">
-        <v>0.207</v>
+        <v>0.4117</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2023</v>
+        <v>0.4696</v>
       </c>
       <c r="V4" t="n">
         <v>0.2113</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9006999999999999</v>
+        <v>1.2308</v>
       </c>
       <c r="E5" t="n">
-        <v>0.236</v>
+        <v>-0.4568</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6647</v>
+        <v>1.6876</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1947</v>
+        <v>3.7682</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5292</v>
+        <v>2.1209</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.3344</v>
+        <v>1.6474</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4448</v>
+        <v>2.7934</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9312</v>
+        <v>1.298</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.4865</v>
+        <v>1.4954</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.25</v>
+        <v>0.9749</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4021</v>
+        <v>0.8228</v>
       </c>
       <c r="O5" t="n">
         <v>0.152</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
         <v>1.9585</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2525</v>
+        <v>0.0554</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2088</v>
+        <v>0.3535</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0437</v>
+        <v>-0.298</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.6136</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.9477</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4936</v>
+        <v>0.9356</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8916</v>
+        <v>2.3603</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.398</v>
+        <v>-1.4247</v>
       </c>
       <c r="G6" t="n">
         <v>0.4279</v>
@@ -922,13 +922,13 @@
         <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.326</v>
+        <v>0.116</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3564</v>
+        <v>0.1123</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0304</v>
+        <v>0.0037</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ONWUKA ONWUKA</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3119</v>
+        <v>0.8089</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9146</v>
+        <v>-1.4859</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6027</v>
+        <v>2.2948</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6369</v>
+        <v>-0.5931</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6427</v>
+        <v>-0.7091</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2795</v>
+        <v>0.1161</v>
       </c>
       <c r="J7" t="n">
-        <v>5.2348</v>
+        <v>0.0559</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1021</v>
+        <v>0.6429</v>
       </c>
       <c r="L7" t="n">
-        <v>5.1327</v>
+        <v>-0.5869</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5979</v>
+        <v>-0.649</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7447</v>
+        <v>-1.352</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1468</v>
+        <v>0.703</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3917</v>
+        <v>2.7419</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0655</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0288</v>
+        <v>0.5099</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0367</v>
+        <v>-0.0094</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.8237</v>
+        <v>0.3139</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3905</v>
+        <v>0.1026</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4332</v>
+        <v>0.2113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>D. ONWUKA ONWUKA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2853</v>
+        <v>0.1561</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1164</v>
+        <v>2.8122</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4017</v>
+        <v>-2.6562</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5931</v>
+        <v>4.6369</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7091</v>
+        <v>-0.6427</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1161</v>
+        <v>5.2795</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0559</v>
+        <v>5.2348</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6429</v>
+        <v>0.1021</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5869</v>
+        <v>5.1327</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.649</v>
+        <v>-0.5979</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.352</v>
+        <v>-0.7447</v>
       </c>
       <c r="O8" t="n">
-        <v>0.703</v>
+        <v>0.1468</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1543</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7419</v>
+        <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0231</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1206</v>
+        <v>-0.0735</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0975</v>
+        <v>-0.0168</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3139</v>
+        <v>-2.8237</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1026</v>
+        <v>-0.3905</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2113</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. LASTRA GONZALEZ</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.305</v>
+        <v>-0.1758</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7416</v>
+        <v>-2.0876</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4367</v>
+        <v>1.9118</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.477</v>
+        <v>-0.2645</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0677</v>
+        <v>0.2664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4093</v>
+        <v>-0.531</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6822</v>
+        <v>0.1824</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.007</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6822</v>
+        <v>-0.8246</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2052</v>
+        <v>-0.4469</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0677</v>
+        <v>-0.7406</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2729</v>
+        <v>0.2937</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.1336</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1958</v>
+        <v>2.9377</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0238</v>
+        <v>0.1309</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0594</v>
+        <v>0.3129</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0356</v>
+        <v>-0.182</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1537</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>D. LASTRA GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2737</v>
+        <v>-0.2515</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0251</v>
+        <v>-0.7416</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7514</v>
+        <v>0.4901</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2645</v>
+        <v>-0.477</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2664</v>
+        <v>-0.0677</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.531</v>
+        <v>-0.4093</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1824</v>
+        <v>-0.6822</v>
       </c>
       <c r="K10" t="n">
-        <v>1.007</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8246</v>
+        <v>-0.6822</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4469</v>
+        <v>0.2052</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7406</v>
+        <v>-0.0677</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2937</v>
+        <v>0.2729</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1958</v>
+        <v>0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9377</v>
+        <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.967</v>
+        <v>0.0297</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6246</v>
+        <v>-0.0594</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3424</v>
+        <v>0.0891</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1537</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.4315</v>
+        <v>-7.558</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.8492</v>
+        <v>-7.8688</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4177</v>
+        <v>0.3107</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2687</v>
@@ -1312,13 +1312,13 @@
         <v>2.7419</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1242</v>
+        <v>0.7493</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7433999999999999</v>
+        <v>0.237</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6192</v>
+        <v>0.5123</v>
       </c>
       <c r="V11" t="n">
         <v>-0.73</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.197699999999999</v>
+        <v>1.7919</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1159</v>
+        <v>-2.522</v>
       </c>
       <c r="F12" t="n">
         <v>4.3137</v>
@@ -1357,10 +1357,10 @@
         <v>7.1193</v>
       </c>
       <c r="H12" t="n">
-        <v>6.489099999999999</v>
+        <v>6.4891</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6302999999999996</v>
+        <v>0.6303000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>14.7392</v>
@@ -1372,13 +1372,13 @@
         <v>-0.2075999999999998</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.619700000000001</v>
+        <v>-7.6197</v>
       </c>
       <c r="N12" t="n">
         <v>-8.4579</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8379000000000001</v>
+        <v>0.8378999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>-5.8755</v>
@@ -1390,13 +1390,13 @@
         <v>15.6679</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4435</v>
+        <v>4.0375</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5995</v>
+        <v>3.1936</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8440000000000001</v>
+        <v>0.8441</v>
       </c>
       <c r="V12" t="n">
         <v>-3.4896</v>
@@ -1405,7 +1405,7 @@
         <v>1.0889</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.5785</v>
+        <v>-4.578499999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5376</v>
+        <v>3.9575</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6118</v>
+        <v>3.4861</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9258</v>
+        <v>0.4714</v>
       </c>
       <c r="G13" t="n">
         <v>3.1249</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9173</v>
+        <v>0.3372</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9326</v>
+        <v>0.8069</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0153</v>
+        <v>-0.4698</v>
       </c>
       <c r="V13" t="n">
         <v>3.0415</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7907</v>
+        <v>2.9549</v>
       </c>
       <c r="E14" t="n">
-        <v>1.882</v>
+        <v>2.3937</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.5613</v>
       </c>
       <c r="G14" t="n">
         <v>1.6252</v>
@@ -1546,13 +1546,13 @@
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3793</v>
+        <v>-0.2151</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9504</v>
+        <v>-0.4388</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.2236</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2178</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7645</v>
+        <v>2.0585</v>
       </c>
       <c r="E15" t="n">
         <v>1.7337</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0308</v>
+        <v>0.3248</v>
       </c>
       <c r="G15" t="n">
         <v>1.5155</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9261</v>
+        <v>-0.6321</v>
       </c>
       <c r="T15" t="n">
         <v>0.1235</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0496</v>
+        <v>-0.7556</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9737</v>
+        <v>1.1872</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0259</v>
+        <v>2.6729</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9995000000000001</v>
+        <v>-1.4858</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.1563</v>
+        <v>1.1858</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.1566</v>
+        <v>-0.4768</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0004</v>
+        <v>1.6626</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.625</v>
+        <v>3.7398</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.2765</v>
+        <v>1.8355</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6515</v>
+        <v>1.9043</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5312</v>
+        <v>-2.5541</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8801</v>
+        <v>-2.3123</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6511</v>
+        <v>-0.2417</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3917</v>
+        <v>1.9585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.546</v>
+        <v>1.9585</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7555</v>
+        <v>-0.7405</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4366</v>
+        <v>-0.6764</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6812</v>
+        <v>-0.0641</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7662</v>
+        <v>-1.2166</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1003</v>
+        <v>-0.3905</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6659</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>A. PEREZ REQUENA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6755</v>
+        <v>0.4847</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1613</v>
+        <v>-0.1159</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4858</v>
+        <v>0.6006</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1858</v>
+        <v>-0.0137</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4768</v>
+        <v>-0.3675</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6626</v>
+        <v>0.3537</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7398</v>
+        <v>0.1217</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8355</v>
+        <v>0.0408</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9043</v>
+        <v>0.0808</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5541</v>
+        <v>-0.1354</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3123</v>
+        <v>-0.4083</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2417</v>
+        <v>0.2729</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9585</v>
+        <v>0.7834</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2521</v>
+        <v>-0.285</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.188</v>
+        <v>-0.2376</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0641</v>
+        <v>-0.0473</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8260999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5931</v>
+        <v>0.2816</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9079</v>
+        <v>1.7032</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3148</v>
+        <v>-1.4217</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0958</v>
@@ -1858,13 +1858,13 @@
         <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1901</v>
+        <v>-0.5017</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0465</v>
+        <v>-0.1582</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2365</v>
+        <v>-0.3435</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8837</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PEREZ REQUENA</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4312</v>
+        <v>-0.0697</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1159</v>
+        <v>-0.2603</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5472</v>
+        <v>0.1906</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0137</v>
+        <v>0.2118</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3675</v>
+        <v>-0.2943</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3537</v>
+        <v>0.5061</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1217</v>
+        <v>2.2878</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0408</v>
+        <v>2.0857</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0808</v>
+        <v>0.2021</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1354</v>
+        <v>-2.076</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4083</v>
+        <v>-2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2729</v>
+        <v>0.304</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7834</v>
+        <v>2.546</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3384</v>
+        <v>-0.7734</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2376</v>
+        <v>-0.4364</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1008</v>
+        <v>-0.337</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4578</v>
+        <v>-0.3287</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7996</v>
+        <v>-0.6973</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3418</v>
+        <v>0.3685</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6891</v>
@@ -2014,13 +2014,13 @@
         <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1604</v>
+        <v>-0.0313</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9113</v>
+        <v>-0.6057</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5673</v>
+        <v>-1.7656</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.344</v>
+        <v>1.1599</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2118</v>
+        <v>-3.1563</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2943</v>
+        <v>-3.1566</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5061</v>
+        <v>0.0004</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2878</v>
+        <v>-1.625</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0857</v>
+        <v>-2.2765</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2021</v>
+        <v>0.6515</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.076</v>
+        <v>-1.5312</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.38</v>
+        <v>-0.8801</v>
       </c>
       <c r="O21" t="n">
-        <v>0.304</v>
+        <v>-0.6511</v>
       </c>
       <c r="P21" t="n">
         <v>-0.3917</v>
@@ -2092,22 +2092,22 @@
         <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.615</v>
+        <v>0.1761</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7433999999999999</v>
+        <v>0.6969</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8716</v>
+        <v>-0.5208</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8837</v>
+        <v>2.7662</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8260999999999999</v>
+        <v>2.1003</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0576</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2715</v>
+        <v>-3.1203</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6966</v>
+        <v>-2.4919</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5749</v>
+        <v>-0.6284</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1405</v>
@@ -2170,13 +2170,13 @@
         <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1897</v>
+        <v>-0.0385</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1012</v>
+        <v>0.1035</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0886</v>
+        <v>-0.142</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5495</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6181</v>
+        <v>-3.967</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6166</v>
+        <v>-5.9697</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9985000000000001</v>
+        <v>2.0028</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.8939</v>
+        <v>-5.7931</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0296</v>
+        <v>-1.7201</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8643</v>
+        <v>-4.073</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3513</v>
+        <v>-5.1316</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4662</v>
+        <v>-1.043</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.885</v>
+        <v>-4.0886</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5427</v>
+        <v>-0.6615</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5634</v>
+        <v>-0.677</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0208</v>
+        <v>0.0156</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R23" t="n">
         <v>2.3502</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1159</v>
+        <v>-0.2107</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3068</v>
+        <v>0.1411</v>
       </c>
       <c r="U23" t="n">
-        <v>0.191</v>
+        <v>-0.3518</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7055</v>
+        <v>-4.0308</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.7884</v>
+        <v>-5.0026</v>
       </c>
       <c r="F24" t="n">
-        <v>2.083</v>
+        <v>0.9718</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.7931</v>
+        <v>-3.8939</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7201</v>
+        <v>-2.0296</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.073</v>
+        <v>-1.8643</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.1316</v>
+        <v>-2.3513</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.043</v>
+        <v>-0.4662</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.0886</v>
+        <v>-1.885</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6615</v>
+        <v>-1.5427</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.677</v>
+        <v>-1.5634</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0156</v>
+        <v>0.0208</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R24" t="n">
         <v>2.3502</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9492</v>
+        <v>-0.5286</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6775</v>
+        <v>-0.6928</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2717</v>
+        <v>0.1642</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.197899999999998</v>
+        <v>-1.1978</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3136</v>
+        <v>-4.313699999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>3.1159</v>
+        <v>3.1158</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.119199999999999</v>
+        <v>-7.119200000000001</v>
       </c>
       <c r="H25" t="n">
         <v>-6.489000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.630300000000001</v>
+        <v>-0.6303000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>7.619799999999999</v>
+        <v>7.6198</v>
       </c>
       <c r="K25" t="n">
         <v>8.457699999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8378999999999994</v>
+        <v>-0.8378999999999996</v>
       </c>
       <c r="M25" t="n">
         <v>-14.7392</v>
@@ -2404,10 +2404,10 @@
         <v>21.5432</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4434</v>
+        <v>-3.4436</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8438999999999999</v>
+        <v>-0.8442000000000001</v>
       </c>
       <c r="U25" t="n">
         <v>-2.5995</v>
